--- a/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
@@ -325,50 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25THA</t>
+          <t>K25DAB</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1252037</t>
+          <t>88637776</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0106869738-044</t>
+          <t>0100109106</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
+          <t>Công Ty Tnhh Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>455455.0</v>
+        <v>208182.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>45545.0</v>
+        <v>20818.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>501000.0</v>
+        <v>229000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -386,6 +386,871 @@
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>K25DAA</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>665446</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0100686209-129</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+        </is>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>143276.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>14328.0</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>157604.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>K25DAA</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>685685</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0100686209-129</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+        </is>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>147791.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>14779.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>162570.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K25DAA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>705628</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0100686209-129</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>175364.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>17366.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>192730.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K25DAA</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>705817</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0100686209-129</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+        </is>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>145582.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>14558.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>160140.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25THB</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>8485</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0106869738-044</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>846799.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>11726.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>858525.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>16123</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0300555450-009</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>545630.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>43650.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>589280.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>24549</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0300555450-009</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>481716.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>38537.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>520253.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>24560</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0300555450-009</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2762</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0300555450-009</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>538222.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>43058.0</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>581280.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>1276830</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>1200912.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>96073.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>1296985.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25TDP</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0319150218</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM KIỂM SOÁT BỆNH TẬT THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>366A Âu Dương Lân, Phường Chánh Hưng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>1448000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
@@ -325,50 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25THA</t>
+          <t>K25TVA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1252037</t>
+          <t>2935738</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0106869738-044</t>
+          <t>0100109106-122</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+          <t>Viettel Hồ Chí Minh- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>455455.0</v>
+        <v>829630.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>45545.0</v>
+        <v>66370.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>501000.0</v>
+        <v>896000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>

--- a/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
@@ -325,50 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TVA</t>
+          <t>K25THA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2935738</t>
+          <t>1252037</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100109106-122</t>
+          <t>0106869738-044</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Viettel Hồ Chí Minh- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>829630.0</v>
+        <v>455455.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>66370.0</v>
+        <v>45545.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>896000.0</v>
+        <v>501000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>

--- a/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
@@ -325,12 +325,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25THA</t>
+          <t>K25TMZ</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1252037</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -340,35 +340,41 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0106869738-044</t>
+          <t>0100108688-008</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
-        </is>
-      </c>
-      <c r="H7" s="6"/>
+          <t>CÔNG TY XĂNG DẦU QUÂN ĐỘI KHU VỰC 4</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>18D Đường Cộng Hòa, phường Tân Sơn Nhất, thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>455455.0</v>
+        <v>648148.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>45545.0</v>
-      </c>
-      <c r="M7" s="13"/>
+        <v>51852.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>501000.0</v>
+        <v>700000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -386,6 +392,249 @@
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>K25TMZ</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>16226</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0100108688-008</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY XĂNG DẦU QUÂN ĐỘI KHU VỰC 4</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>18D Đường Cộng Hòa, phường Tân Sơn Nhất, thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>648148.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>51852.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>700000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>K25TMZ</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>16227</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0100108688-008</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY XĂNG DẦU QUÂN ĐỘI KHU VỰC 4</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>18D Đường Cộng Hòa, phường Tân Sơn Nhất, thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K25THA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>1233524</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0106869738-044</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CTy TNHH TM &amp; XD Đại Thành Công</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>152728.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>15273.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>168001.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
@@ -325,12 +325,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TMZ</t>
+          <t>K25THA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>1264350</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -340,41 +340,35 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100108688-008</t>
+          <t>0106869738-044</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY XĂNG DẦU QUÂN ĐỘI KHU VỰC 4</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>18D Đường Cộng Hòa, phường Tân Sơn Nhất, thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>648148.0</v>
+        <v>218182.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>51852.0</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>21818.0</v>
+      </c>
+      <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>700000.0</v>
+        <v>240000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +402,54 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TMZ</t>
+          <t>K25TDE</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>05/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0100108688-008</t>
+          <t>0109153068</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY XĂNG DẦU QUÂN ĐỘI KHU VỰC 4</t>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>18D Đường Cộng Hòa, phường Tân Sơn Nhất, thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>648148.0</v>
+        <v>21740.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>51852.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>2174.0</v>
+      </c>
+      <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>700000.0</v>
+        <v>23914.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -471,7 +463,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị điều chỉnh</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -491,56 +483,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25TMZ</t>
+          <t>K25TDE</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0100108688-008</t>
+          <t>0109153068</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY XĂNG DẦU QUÂN ĐỘI KHU VỰC 4</t>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>18D Đường Cộng Hòa, phường Tân Sơn Nhất, thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>462963.0</v>
+        <v>57030.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>5703.0</v>
+      </c>
+      <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>500000.0</v>
+        <v>62733.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -554,7 +544,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị điều chỉnh</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -574,50 +564,54 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>K25THA</t>
+          <t>K25TDE</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1233524</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>19/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0106869738-044</t>
+          <t>0109153068</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
-        </is>
-      </c>
-      <c r="H10" s="6"/>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CTy TNHH TM &amp; XD Đại Thành Công</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>152728.0</v>
+        <v>55210.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>15273.0</v>
+        <v>5521.0</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>168001.0</v>
+        <v>60731.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -631,10 +625,1488 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
+          <t>Hóa đơn đã bị điều chỉnh</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K25TDE</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>26/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0109153068</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>148075.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>11847.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>159922.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn đã bị thay thế</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25TDE</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>26/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0109153068</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>148075.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>11846.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>159921.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25TDE</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0109153068</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>-21736.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>-2174.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>-23910.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25TDE</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0109153068</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>-57034.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>-5703.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>-62737.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25TDE</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0109153068</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>-55228.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>-5521.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>-60749.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25TDE</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0109153068</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>136478.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>10918.0</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>147396.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="S10" s="6" t="inlineStr">
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25TDE</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2842</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>0109153068</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ONE MOUNT DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 3, Tòa văn phòng T26, KĐT Times City, 458 Minh Khai, Phường Vĩnh Tuy, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>59725.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>4779.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>64504.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>445351</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>2777778.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>222222.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>456652</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>2777778.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>222222.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>457491</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>1851852.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>148148.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>2000000.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>461054</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>2314815.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>185185.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>2500000.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>481860</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>2777778.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>222222.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>485164</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>827778.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>66222.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>894000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>485836</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>2777778.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>222222.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>489861</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>1685185.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>134815.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>1820000.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>491682</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>2777778.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>222222.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>K25TLB</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>495153</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3501740836</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>2777778.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>222222.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>K25TAA</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>568379</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3600247325</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV PETROLIMEX ĐỒNG NAI</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Số 104, đường Hà Huy Giáp, Phường Trấn Biên, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>2777778.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>222222.0</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
@@ -325,54 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TXT</t>
+          <t>K25TVA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>2935738</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>21/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0300555450-009</t>
+          <t>0100109106-122</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
-        </is>
-      </c>
+          <t>Viettel Hồ Chí Minh- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>462963.0</v>
+        <v>829630.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>37037.0</v>
+        <v>66370.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>500000.0</v>
+        <v>896000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -406,56 +402,50 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TBC</t>
+          <t>K25TAA</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>299770</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>21/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0100150619-006</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CONG TY TNHH MTV VUON PHO VUNG TAU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>462963.0</v>
+        <v>100000.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>10000.0</v>
+      </c>
+      <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>500000.0</v>
+        <v>110000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -489,56 +479,50 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25TBC</t>
+          <t>K25TAA</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>311087</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0100150619-150</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Vũng Tàu - Côn Đảo</t>
+        </is>
+      </c>
+      <c r="H9" s="6"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CONG TY TNHH MTV VUON PHO VUNG TAU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>462963.0</v>
+        <v>20000.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>2000.0</v>
+      </c>
+      <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>500000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -572,56 +556,50 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TAA</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>482691</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0100150619-150</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Vũng Tàu - Côn Đảo</t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CONG TY TNHH MTV VUON PHO VUNG TAU</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>462963.0</v>
+        <v>20000.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>2000.0</v>
+      </c>
+      <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>500000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -655,56 +633,50 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>K25TLK</t>
+          <t>K25TOT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>484334</t>
+          <t>4865234</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3501740836</t>
+          <t>0101778163-001</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Số 54A đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+        </is>
+      </c>
+      <c r="H11" s="6"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>Cong Ty TNHH Mot Thanh Vien Vuon Pho Vung Tau</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>462963.0</v>
+        <v>305909.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>37037.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>30591.0</v>
+      </c>
+      <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>500000.0</v>
+        <v>336500.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -722,6 +694,83 @@
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25TOT</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>4865236</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0101778163-001</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+        </is>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Cong Ty TNHH Mot Thanh Vien Vuon Pho Vung Tau</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>335909.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>32391.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>368300.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
@@ -325,50 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TVA</t>
+          <t>K25DAA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2935738</t>
+          <t>662401</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100109106-122</t>
+          <t>0100686209-129</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Viettel Hồ Chí Minh- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đông Dương Vũng Tàu</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>829630.0</v>
+        <v>61000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>66370.0</v>
+        <v>6100.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>896000.0</v>
+        <v>67100.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -382,7 +382,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị điều chỉnh</t>
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
@@ -402,50 +402,50 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TAA</t>
+          <t>K25DAA</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>789387</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>21/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0100150619-006</t>
+          <t>0100686209-129</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Bà Rịa - Vũng Tàu</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CONG TY TNHH MTV VUON PHO VUNG TAU</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đông Dương Vũng Tàu</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>100000.0</v>
+        <v>-909.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>10000.0</v>
+        <v>-91.0</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>110000.0</v>
+        <v>-1000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -459,7 +459,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn điều chỉnh</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -479,50 +479,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25TAA</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>33705</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0100150619-150</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Vũng Tàu - Côn Đảo</t>
-        </is>
-      </c>
-      <c r="H9" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CONG TY TNHH MTV VUON PHO VUNG TAU</t>
+          <t>Công ty TNHH Đông Dương Vũng tàu</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>20000.0</v>
+        <v>925926.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>2000.0</v>
+        <v>74074.0</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>22000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -556,50 +560,54 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>K25TAA</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0100150619-150</t>
+          <t>0300555450-009</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Vũng Tàu - Côn Đảo</t>
-        </is>
-      </c>
-      <c r="H10" s="6"/>
+          <t>CHI NHÁNH PETROLIMEX VŨNG TÀU - CÔNG TY TNHH MTV PETROLIMEX SÀI GÒN</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CONG TY TNHH MTV VUON PHO VUNG TAU</t>
+          <t>Công ty TNHH Đông Dương Vũng tàu</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>20000.0</v>
+        <v>925926.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>2000.0</v>
+        <v>74074.0</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>22000.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -633,50 +641,50 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>K25TOT</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>4865234</t>
+          <t>1364700</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>0101778163-001</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
         </is>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Cong Ty TNHH Mot Thanh Vien Vuon Pho Vung Tau</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đông Dương Vũng Tàu</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>305909.0</v>
+        <v>242704.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>30591.0</v>
+        <v>19416.0</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>336500.0</v>
+        <v>262120.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -710,50 +718,52 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>K25TOT</t>
+          <t>K25TAB</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>4865236</t>
+          <t>266431</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>0101778163-001</t>
+          <t>0301103908-045</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
         </is>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Cong Ty TNHH Mot Thanh Vien Vuon Pho Vung Tau</t>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>335909.0</v>
+        <v>14000.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>32391.0</v>
+        <v>1400.0</v>
       </c>
       <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O12" s="13" t="n">
-        <v>368300.0</v>
+        <v>15400.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -771,6 +781,1586 @@
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>268085</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>273724</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>274579</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>274580</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>274581</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>275358</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>277329</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>279409</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H20" s="6"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>279715</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>279793</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>280442</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>280443</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>286798</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>286799</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>287017</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>26/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>287652</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>287653</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>291170</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>140000.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>154000.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>293046</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>295406</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH DONG DUONG VUNG TAU</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>1400.0</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>15400.0</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuKhongMa.xlsx
@@ -325,12 +325,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25DAB</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>205108</t>
+          <t>88638062</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -340,35 +340,35 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100111948-043</t>
+          <t>0100109106</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN CÔNG THƯƠNG VIỆT NAM - CHI NHÁNH BÀ RỊA - VŨNG TÀU</t>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>35000.0</v>
+        <v>90909.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>3500.0</v>
+        <v>9091.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>38500.0</v>
+        <v>100000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -386,6 +386,6265 @@
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>88638675</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>88639562</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>775464.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>77546.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>853010.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>88645769</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>93273.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>9327.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>102600.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>88647505</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>109091.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>10909.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>88649430</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>153417.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>15342.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>168759.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>88649799</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>109091.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>10909.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>88650014</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>88653416</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>156962.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>15696.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>172658.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>88656929</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>88659237</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>244154.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>24415.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>268569.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>88662392</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>128874.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>12887.0</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>141761.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>88662399</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>236364.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>23636.0</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>260000.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>88666567</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H20" s="6"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>88667402</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>88671249</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>88677847</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>88678350</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>454545.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>45455.0</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>88681947</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>K25DAB</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>88682233</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>0100109106</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>K25TAA</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>31148</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>0100150619-006</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>3208319.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>320835.0</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>3529154.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>6120139</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>6124996</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>6153564</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>27750.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>2775.0</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>30525.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>6219713</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>50000.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>5000.0</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>55000.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>6306198</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>05/10/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>2200.0</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>6331052</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>6332268</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>6333151</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>6355361</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>24777.0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>2478.0</v>
+      </c>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>27255.0</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>6365908</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>6369483</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>6397205</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>6431943</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H40" s="6"/>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>6436511</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H41" s="6"/>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>6488032</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H42" s="6"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>6537248</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H43" s="6"/>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>6539973</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>6721233</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>6724426</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>K25TOT</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>4831144</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>0101778163-001</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+        </is>
+      </c>
+      <c r="H47" s="6"/>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Cong Ty TNHHThe Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>269454.0</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>25546.0</v>
+      </c>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13" t="n">
+        <v>295000.0</v>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>K25TOT</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>4844657</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>0101778163-001</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+        </is>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>Cong Ty TNHH  The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="n">
+        <v>909091.0</v>
+      </c>
+      <c r="L48" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>K25TOT</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>4844658</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>0101778163-001</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+        </is>
+      </c>
+      <c r="H49" s="6"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Cong Ty TNHH  The Forum Education VietNam</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>336364.0</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>33636.0</v>
+      </c>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13" t="n">
+        <v>370000.0</v>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>K25TOT</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>4844902</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>0101778163-001</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+        </is>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>272727.0</v>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>27273.0</v>
+      </c>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q50" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>K25TOT</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>4857081</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>0101778163-001</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+        </is>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>30000.0</v>
+      </c>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13" t="n">
+        <v>330000.0</v>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>K25TOT</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>4857090</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>0101778163-001</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Công Ty Cổ Phần Viễn Thông FPT</t>
+        </is>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="n">
+        <v>318182.0</v>
+      </c>
+      <c r="L52" s="13" t="n">
+        <v>31818.0</v>
+      </c>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13" t="n">
+        <v>350000.0</v>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q52" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>K25TMB</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>4079504</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>0102325399</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN HÀNG KHÔNG VIETJET</t>
+        </is>
+      </c>
+      <c r="H53" s="6"/>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="n">
+        <v>2149000.0</v>
+      </c>
+      <c r="L53" s="13" t="n">
+        <v>171920.0</v>
+      </c>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>2439920.0</v>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>K25TMB</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>4080806</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>0102325399</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN HÀNG KHÔNG VIETJET</t>
+        </is>
+      </c>
+      <c r="H54" s="6"/>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>2149000.0</v>
+      </c>
+      <c r="L54" s="13" t="n">
+        <v>171920.0</v>
+      </c>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
+        <v>2439920.0</v>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>K25TMB</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>4108146</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>05/10/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>0102325399</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN HÀNG KHÔNG VIETJET</t>
+        </is>
+      </c>
+      <c r="H55" s="6"/>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="n">
+        <v>1849000.0</v>
+      </c>
+      <c r="L55" s="13" t="n">
+        <v>147920.0</v>
+      </c>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>2115920.0</v>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>K25TMB</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>4162593</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>0102325399</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN HÀNG KHÔNG VIETJET</t>
+        </is>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="n">
+        <v>2309000.0</v>
+      </c>
+      <c r="L56" s="13" t="n">
+        <v>184720.0</v>
+      </c>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="13" t="n">
+        <v>2612720.0</v>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>K25TMB</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>4327665</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>0102325399</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN HÀNG KHÔNG VIETJET</t>
+        </is>
+      </c>
+      <c r="H57" s="6"/>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="n">
+        <v>1260000.0</v>
+      </c>
+      <c r="L57" s="13" t="n">
+        <v>100800.0</v>
+      </c>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>1479800.0</v>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>K25TMB</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>4327673</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>0102325399</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN HÀNG KHÔNG VIETJET</t>
+        </is>
+      </c>
+      <c r="H58" s="6"/>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>1879000.0</v>
+      </c>
+      <c r="L58" s="13" t="n">
+        <v>150320.0</v>
+      </c>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="13" t="n">
+        <v>2148320.0</v>
+      </c>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>K25TMB</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>4371349</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>0102325399</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN HÀNG KHÔNG VIETJET</t>
+        </is>
+      </c>
+      <c r="H59" s="6"/>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>1690000.0</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>135200.0</v>
+      </c>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>1944200.0</v>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>10061794</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="n">
+        <v>68858.0</v>
+      </c>
+      <c r="L60" s="13" t="n">
+        <v>6886.0</v>
+      </c>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13" t="n">
+        <v>75744.0</v>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q60" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>10102940</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H61" s="6"/>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="n">
+        <v>244240.0</v>
+      </c>
+      <c r="L61" s="13" t="n">
+        <v>24424.0</v>
+      </c>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13" t="n">
+        <v>268664.0</v>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>10132498</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H62" s="6"/>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>290500.0</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>29050.0</v>
+      </c>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13" t="n">
+        <v>319550.0</v>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q62" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>10201070</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H63" s="6"/>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>84160.0</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>8416.0</v>
+      </c>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13" t="n">
+        <v>92576.0</v>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S63" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>10265692</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H64" s="6"/>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>250580.0</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>25058.0</v>
+      </c>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13" t="n">
+        <v>275638.0</v>
+      </c>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S64" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>10283642</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H65" s="6"/>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>196840.0</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>19684.0</v>
+      </c>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13" t="n">
+        <v>216524.0</v>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>10325845</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H66" s="6"/>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>98500.0</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>9850.0</v>
+      </c>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13" t="n">
+        <v>108350.0</v>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S66" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>10376460</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H67" s="6"/>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>363360.0</v>
+      </c>
+      <c r="L67" s="13" t="n">
+        <v>36336.0</v>
+      </c>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13" t="n">
+        <v>399696.0</v>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q67" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>10417975</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H68" s="6"/>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>452200.0</v>
+      </c>
+      <c r="L68" s="13" t="n">
+        <v>45220.0</v>
+      </c>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13" t="n">
+        <v>497420.0</v>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>10449481</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H69" s="6"/>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>93440.0</v>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>9344.0</v>
+      </c>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13" t="n">
+        <v>102784.0</v>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>10473698</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H70" s="6"/>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="n">
+        <v>155220.0</v>
+      </c>
+      <c r="L70" s="13" t="n">
+        <v>15522.0</v>
+      </c>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13" t="n">
+        <v>170742.0</v>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>10522942</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H71" s="6"/>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="n">
+        <v>323320.0</v>
+      </c>
+      <c r="L71" s="13" t="n">
+        <v>32332.0</v>
+      </c>
+      <c r="M71" s="13"/>
+      <c r="N71" s="13"/>
+      <c r="O71" s="13" t="n">
+        <v>355652.0</v>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>10789589</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="n">
+        <v>30000.0</v>
+      </c>
+      <c r="L72" s="13" t="n">
+        <v>3000.0</v>
+      </c>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13"/>
+      <c r="O72" s="13" t="n">
+        <v>33000.0</v>
+      </c>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q72" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>10789590</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H73" s="6"/>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="n">
+        <v>358600.0</v>
+      </c>
+      <c r="L73" s="13" t="n">
+        <v>35860.0</v>
+      </c>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13"/>
+      <c r="O73" s="13" t="n">
+        <v>394460.0</v>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q73" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S73" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>K25TTP</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>10806974</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>0102744865</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP TIÊN PHONG</t>
+        </is>
+      </c>
+      <c r="H74" s="6"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="n">
+        <v>370760.0</v>
+      </c>
+      <c r="L74" s="13" t="n">
+        <v>37076.0</v>
+      </c>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="13" t="n">
+        <v>407836.0</v>
+      </c>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q74" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S74" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>K25THA</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>1249737</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>0106869738-044</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H75" s="6"/>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="n">
+        <v>163454.0</v>
+      </c>
+      <c r="L75" s="13" t="n">
+        <v>16345.0</v>
+      </c>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="13" t="n">
+        <v>179799.0</v>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q75" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>K25THA</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>1281054</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>0106869738-044</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H76" s="6"/>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="n">
+        <v>2367937.0</v>
+      </c>
+      <c r="L76" s="13" t="n">
+        <v>236794.0</v>
+      </c>
+      <c r="M76" s="13"/>
+      <c r="N76" s="13"/>
+      <c r="O76" s="13" t="n">
+        <v>2604731.0</v>
+      </c>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q76" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S76" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>1298010</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H77" s="6"/>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH The FORUM EDUCATION</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="n">
+        <v>4561074.0</v>
+      </c>
+      <c r="L77" s="13" t="n">
+        <v>364886.0</v>
+      </c>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="13" t="n">
+        <v>4925960.0</v>
+      </c>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q77" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S77" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>1298016</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H78" s="6"/>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="n">
+        <v>908208.0</v>
+      </c>
+      <c r="L78" s="13" t="n">
+        <v>72657.0</v>
+      </c>
+      <c r="M78" s="13"/>
+      <c r="N78" s="13"/>
+      <c r="O78" s="13" t="n">
+        <v>980865.0</v>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q78" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>73.0</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>1298128</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H79" s="6"/>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="n">
+        <v>2317266.0</v>
+      </c>
+      <c r="L79" s="13" t="n">
+        <v>185381.0</v>
+      </c>
+      <c r="M79" s="13"/>
+      <c r="N79" s="13"/>
+      <c r="O79" s="13" t="n">
+        <v>2502647.0</v>
+      </c>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q79" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>1301459</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H80" s="6"/>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="n">
+        <v>3612798.0</v>
+      </c>
+      <c r="L80" s="13" t="n">
+        <v>289024.0</v>
+      </c>
+      <c r="M80" s="13"/>
+      <c r="N80" s="13"/>
+      <c r="O80" s="13" t="n">
+        <v>3901822.0</v>
+      </c>
+      <c r="P80" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q80" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>1303233</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H81" s="6"/>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education Vietnam</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="n">
+        <v>2778048.0</v>
+      </c>
+      <c r="L81" s="13" t="n">
+        <v>222244.0</v>
+      </c>
+      <c r="M81" s="13"/>
+      <c r="N81" s="13"/>
+      <c r="O81" s="13" t="n">
+        <v>3000292.0</v>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q81" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>1303235</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H82" s="6"/>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K82" s="13" t="n">
+        <v>3450300.0</v>
+      </c>
+      <c r="L82" s="13" t="n">
+        <v>276024.0</v>
+      </c>
+      <c r="M82" s="13"/>
+      <c r="N82" s="13"/>
+      <c r="O82" s="13" t="n">
+        <v>3726324.0</v>
+      </c>
+      <c r="P82" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q82" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>77.0</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>1303237</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H83" s="6"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K83" s="13" t="n">
+        <v>2662296.0</v>
+      </c>
+      <c r="L83" s="13" t="n">
+        <v>212984.0</v>
+      </c>
+      <c r="M83" s="13"/>
+      <c r="N83" s="13"/>
+      <c r="O83" s="13" t="n">
+        <v>2875280.0</v>
+      </c>
+      <c r="P83" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q83" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>K25TDA</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>1309568</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>0300951119-010</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H84" s="6"/>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH The Forum EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K84" s="13" t="n">
+        <v>149142.0</v>
+      </c>
+      <c r="L84" s="13" t="n">
+        <v>11931.0</v>
+      </c>
+      <c r="M84" s="13"/>
+      <c r="N84" s="13"/>
+      <c r="O84" s="13" t="n">
+        <v>161073.0</v>
+      </c>
+      <c r="P84" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q84" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>K25TAC</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>16240</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>0301103908</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Hội sở</t>
+        </is>
+      </c>
+      <c r="H85" s="6"/>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="n">
+        <v>692084.0</v>
+      </c>
+      <c r="L85" s="13" t="n">
+        <v>69208.0</v>
+      </c>
+      <c r="M85" s="13"/>
+      <c r="N85" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>761292.0</v>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q85" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>K25TAB</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>291240</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>0301103908-045</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="H86" s="6"/>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>CTY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="L86" s="13" t="n">
+        <v>12000.0</v>
+      </c>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O86" s="13" t="n">
+        <v>132000.0</v>
+      </c>
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q86" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>K25TAA</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>1813024</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>3500101386</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H87" s="6"/>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="n">
+        <v>202000.0</v>
+      </c>
+      <c r="L87" s="13" t="n">
+        <v>10100.0</v>
+      </c>
+      <c r="M87" s="13"/>
+      <c r="N87" s="13" t="n">
+        <v>20200.0</v>
+      </c>
+      <c r="O87" s="13" t="n">
+        <v>232300.0</v>
+      </c>
+      <c r="P87" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q87" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S87" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>K25TAA</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>1833123</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>3500101386</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H88" s="6"/>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="n">
+        <v>161600.0</v>
+      </c>
+      <c r="L88" s="13" t="n">
+        <v>8080.0</v>
+      </c>
+      <c r="M88" s="13"/>
+      <c r="N88" s="13" t="n">
+        <v>16160.0</v>
+      </c>
+      <c r="O88" s="13" t="n">
+        <v>185840.0</v>
+      </c>
+      <c r="P88" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q88" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S88" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>
